--- a/VibeProject1/Assets/Table/Enemy/EnemyStats.xlsx
+++ b/VibeProject1/Assets/Table/Enemy/EnemyStats.xlsx
@@ -466,8 +466,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marauder</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>60</v>
@@ -495,8 +497,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>90</v>
@@ -524,8 +528,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adversary</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>50</v>
@@ -584,8 +590,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marauder</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
@@ -595,8 +603,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -606,8 +616,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adversary</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -643,8 +655,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marauder</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -653,8 +667,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -663,8 +679,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adversary</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
